--- a/analise_eua/tecnologia/google/googl_10q.xlsx
+++ b/analise_eua/tecnologia/google/googl_10q.xlsx
@@ -435,65 +435,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -504,60 +507,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>55911</v>
+      </c>
+      <c r="C2" t="n">
         <v>38063</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>23090</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>21036</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>23264</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>19959</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>27225</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>24493</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>30702</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>25929</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>25924</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>21984</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>17936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>20886</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>23719</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>23630</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>26622</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>20129</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>17742</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>19644</v>
       </c>
     </row>
@@ -568,60 +574,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>186563</v>
+      </c>
+      <c r="C3" t="n">
         <v>88777</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>75406</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>74112</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>72064</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>73271</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>73500</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>83597</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>89233</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>92403</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>89178</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>94275</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>107061</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>113084</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>118284</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>112233</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>108482</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>112467</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>103338</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>97585</v>
       </c>
     </row>
@@ -632,60 +641,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>242474</v>
+      </c>
+      <c r="C4" t="n">
         <v>126840</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>98496</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>95148</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>95328</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>93230</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>100725</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>108090</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>119935</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>118332</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>115102</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>116259</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>124997</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>133970</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>142003</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>135863</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>135104</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>132596</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>121080</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>117229</v>
       </c>
     </row>
@@ -696,1795 +708,1879 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>69175</v>
+      </c>
+      <c r="C5" t="n">
         <v>62999</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>57148</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>55048</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>51000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>49104</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>47087</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>44552</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>41020</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>38804</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>36036</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>34697</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>35707</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>34703</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>34047</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>31967</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>28006</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>24925</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>21201</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>21825</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Other Assets, Current</t>
+          <t>Inventory, Net</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23914</v>
+        <v>9991</v>
       </c>
       <c r="C6" t="n">
-        <v>18303</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>16020</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>15724</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>15207</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>14183</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>12829</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>12398</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9421</v>
+        <v>2957</v>
       </c>
       <c r="K6" t="n">
-        <v>8532</v>
+        <v>2231</v>
       </c>
       <c r="L6" t="n">
-        <v>10518</v>
+        <v>2315</v>
       </c>
       <c r="M6" t="n">
-        <v>8321</v>
+        <v>3156</v>
       </c>
       <c r="N6" t="n">
-        <v>6892</v>
+        <v>1980</v>
       </c>
       <c r="O6" t="n">
-        <v>6029</v>
+        <v>1369</v>
       </c>
       <c r="P6" t="n">
-        <v>6076</v>
+        <v>1278</v>
       </c>
       <c r="Q6" t="n">
-        <v>7646</v>
+        <v>907</v>
       </c>
       <c r="R6" t="n">
-        <v>5425</v>
+        <v>888</v>
       </c>
       <c r="S6" t="n">
-        <v>5579</v>
+        <v>835</v>
       </c>
       <c r="T6" t="n">
-        <v>5165</v>
+        <v>815</v>
+      </c>
+      <c r="U6" t="n">
+        <v>889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Assets, Current</t>
+          <t>Other Assets, Current</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213753</v>
+        <v>21884</v>
       </c>
       <c r="C7" t="n">
-        <v>173947</v>
+        <v>23914</v>
       </c>
       <c r="D7" t="n">
-        <v>166216</v>
+        <v>18303</v>
       </c>
       <c r="E7" t="n">
-        <v>162052</v>
+        <v>16020</v>
       </c>
       <c r="F7" t="n">
-        <v>157541</v>
+        <v>15724</v>
       </c>
       <c r="G7" t="n">
-        <v>161995</v>
+        <v>15207</v>
       </c>
       <c r="H7" t="n">
-        <v>165471</v>
+        <v>14183</v>
       </c>
       <c r="I7" t="n">
-        <v>176310</v>
+        <v>12829</v>
       </c>
       <c r="J7" t="n">
-        <v>168788</v>
+        <v>12398</v>
       </c>
       <c r="K7" t="n">
-        <v>161985</v>
+        <v>9421</v>
       </c>
       <c r="L7" t="n">
-        <v>166109</v>
+        <v>8532</v>
       </c>
       <c r="M7" t="n">
-        <v>172371</v>
+        <v>10518</v>
       </c>
       <c r="N7" t="n">
-        <v>177853</v>
+        <v>8321</v>
       </c>
       <c r="O7" t="n">
-        <v>184110</v>
+        <v>6892</v>
       </c>
       <c r="P7" t="n">
-        <v>175697</v>
+        <v>6029</v>
       </c>
       <c r="Q7" t="n">
-        <v>172137</v>
+        <v>6076</v>
       </c>
       <c r="R7" t="n">
-        <v>164369</v>
+        <v>7646</v>
       </c>
       <c r="S7" t="n">
-        <v>149069</v>
+        <v>5425</v>
       </c>
       <c r="T7" t="n">
-        <v>147018</v>
+        <v>5579</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Non-marketable Securities</t>
+          <t>Assets, Current</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106946</v>
+        <v>343524</v>
       </c>
       <c r="C8" t="n">
-        <v>63800</v>
+        <v>213753</v>
       </c>
       <c r="D8" t="n">
-        <v>52574</v>
+        <v>173947</v>
       </c>
       <c r="E8" t="n">
-        <v>51029</v>
+        <v>166216</v>
       </c>
       <c r="F8" t="n">
-        <v>36177</v>
+        <v>162052</v>
       </c>
       <c r="G8" t="n">
-        <v>34172</v>
+        <v>157541</v>
       </c>
       <c r="H8" t="n">
-        <v>33994</v>
+        <v>161995</v>
       </c>
       <c r="I8" t="n">
-        <v>30907</v>
+        <v>165471</v>
       </c>
       <c r="J8" t="n">
-        <v>31224</v>
+        <v>176310</v>
       </c>
       <c r="K8" t="n">
-        <v>31213</v>
+        <v>168788</v>
       </c>
       <c r="L8" t="n">
-        <v>30419</v>
+        <v>161985</v>
       </c>
       <c r="M8" t="n">
-        <v>30665</v>
+        <v>166109</v>
       </c>
       <c r="N8" t="n">
-        <v>30544</v>
+        <v>172371</v>
       </c>
       <c r="O8" t="n">
-        <v>26101</v>
+        <v>177853</v>
       </c>
       <c r="P8" t="n">
-        <v>25532</v>
+        <v>184110</v>
       </c>
       <c r="Q8" t="n">
-        <v>25294</v>
+        <v>175697</v>
       </c>
       <c r="R8" t="n">
-        <v>14656</v>
+        <v>172137</v>
       </c>
       <c r="S8" t="n">
-        <v>12961</v>
+        <v>164369</v>
       </c>
       <c r="T8" t="n">
-        <v>12367</v>
+        <v>149069</v>
+      </c>
+      <c r="U8" t="n">
+        <v>147018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Assets, Net</t>
+          <t>Non-marketable Securities</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1995</v>
+        <v>131461</v>
       </c>
       <c r="C9" t="n">
-        <v>10331</v>
+        <v>106946</v>
       </c>
       <c r="D9" t="n">
-        <v>19289</v>
+        <v>63800</v>
       </c>
       <c r="E9" t="n">
-        <v>18386</v>
+        <v>52574</v>
       </c>
       <c r="F9" t="n">
-        <v>15915</v>
+        <v>51029</v>
       </c>
       <c r="G9" t="n">
-        <v>14958</v>
+        <v>36177</v>
       </c>
       <c r="H9" t="n">
-        <v>11687</v>
+        <v>34172</v>
       </c>
       <c r="I9" t="n">
-        <v>10983</v>
+        <v>33994</v>
       </c>
       <c r="J9" t="n">
-        <v>9357</v>
+        <v>30907</v>
       </c>
       <c r="K9" t="n">
-        <v>6885</v>
+        <v>31224</v>
       </c>
       <c r="L9" t="n">
-        <v>2991</v>
+        <v>31213</v>
       </c>
       <c r="M9" t="n">
-        <v>1490</v>
+        <v>30419</v>
       </c>
       <c r="N9" t="n">
-        <v>1388</v>
+        <v>30665</v>
       </c>
       <c r="O9" t="n">
-        <v>1195</v>
+        <v>30544</v>
       </c>
       <c r="P9" t="n">
-        <v>1153</v>
+        <v>26101</v>
       </c>
       <c r="Q9" t="n">
-        <v>1129</v>
+        <v>25532</v>
       </c>
       <c r="R9" t="n">
-        <v>972</v>
+        <v>25294</v>
       </c>
       <c r="S9" t="n">
-        <v>895</v>
+        <v>14656</v>
       </c>
       <c r="T9" t="n">
-        <v>730</v>
+        <v>12961</v>
+      </c>
+      <c r="U9" t="n">
+        <v>12367</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Property, Plant, and Equipment and Finance Lease Right-of-Use Asset, after Accumulated Depreciation and Amortization</t>
+          <t>Deferred Income Tax Assets, Net</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>281020</v>
+        <v>1448</v>
       </c>
       <c r="C10" t="n">
-        <v>223787</v>
+        <v>1995</v>
       </c>
       <c r="D10" t="n">
-        <v>203231</v>
+        <v>10331</v>
       </c>
       <c r="E10" t="n">
-        <v>185062</v>
+        <v>19289</v>
       </c>
       <c r="F10" t="n">
-        <v>161270</v>
+        <v>18386</v>
       </c>
       <c r="G10" t="n">
-        <v>151155</v>
+        <v>15915</v>
       </c>
       <c r="H10" t="n">
-        <v>143182</v>
+        <v>14958</v>
       </c>
       <c r="I10" t="n">
-        <v>125705</v>
+        <v>11687</v>
       </c>
       <c r="J10" t="n">
-        <v>121208</v>
+        <v>10983</v>
       </c>
       <c r="K10" t="n">
-        <v>117560</v>
+        <v>9357</v>
       </c>
       <c r="L10" t="n">
-        <v>108363</v>
+        <v>6885</v>
       </c>
       <c r="M10" t="n">
-        <v>106223</v>
+        <v>2991</v>
       </c>
       <c r="N10" t="n">
-        <v>104218</v>
+        <v>1490</v>
       </c>
       <c r="O10" t="n">
-        <v>94631</v>
+        <v>1388</v>
       </c>
       <c r="P10" t="n">
-        <v>91697</v>
+        <v>1195</v>
       </c>
       <c r="Q10" t="n">
-        <v>87606</v>
+        <v>1153</v>
       </c>
       <c r="R10" t="n">
-        <v>81636</v>
+        <v>1129</v>
       </c>
       <c r="S10" t="n">
-        <v>78748</v>
+        <v>972</v>
       </c>
       <c r="T10" t="n">
-        <v>76747</v>
+        <v>895</v>
+      </c>
+      <c r="U10" t="n">
+        <v>730</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Right-of-Use Asset</t>
+          <t>Property, Plant, and Equipment and Finance Lease Right-of-Use Asset, after Accumulated Depreciation and Amortization</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15509</v>
+        <v>321212</v>
       </c>
       <c r="C11" t="n">
-        <v>14524</v>
+        <v>281020</v>
       </c>
       <c r="D11" t="n">
-        <v>14255</v>
+        <v>223787</v>
       </c>
       <c r="E11" t="n">
-        <v>13722</v>
+        <v>203231</v>
       </c>
       <c r="F11" t="n">
-        <v>13561</v>
+        <v>185062</v>
       </c>
       <c r="G11" t="n">
-        <v>13606</v>
+        <v>161270</v>
       </c>
       <c r="H11" t="n">
-        <v>13768</v>
+        <v>151155</v>
       </c>
       <c r="I11" t="n">
-        <v>14199</v>
+        <v>143182</v>
       </c>
       <c r="J11" t="n">
-        <v>14469</v>
+        <v>125705</v>
       </c>
       <c r="K11" t="n">
-        <v>14447</v>
+        <v>121208</v>
       </c>
       <c r="L11" t="n">
-        <v>13677</v>
+        <v>117560</v>
       </c>
       <c r="M11" t="n">
-        <v>13398</v>
+        <v>108363</v>
       </c>
       <c r="N11" t="n">
-        <v>12992</v>
+        <v>106223</v>
       </c>
       <c r="O11" t="n">
-        <v>12918</v>
+        <v>104218</v>
       </c>
       <c r="P11" t="n">
-        <v>12978</v>
+        <v>94631</v>
       </c>
       <c r="Q11" t="n">
-        <v>12598</v>
+        <v>91697</v>
       </c>
       <c r="R11" t="n">
-        <v>11946</v>
+        <v>87606</v>
       </c>
       <c r="S11" t="n">
-        <v>11567</v>
+        <v>81636</v>
       </c>
       <c r="T11" t="n">
-        <v>11219</v>
+        <v>78748</v>
+      </c>
+      <c r="U11" t="n">
+        <v>76747</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Operating Lease, Right-of-Use Asset</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57774</v>
+        <v>17694</v>
       </c>
       <c r="C12" t="n">
-        <v>33269</v>
+        <v>15509</v>
       </c>
       <c r="D12" t="n">
-        <v>32335</v>
+        <v>14524</v>
       </c>
       <c r="E12" t="n">
-        <v>32173</v>
+        <v>14255</v>
       </c>
       <c r="F12" t="n">
-        <v>31935</v>
+        <v>13722</v>
       </c>
       <c r="G12" t="n">
-        <v>29185</v>
+        <v>13561</v>
       </c>
       <c r="H12" t="n">
-        <v>29183</v>
+        <v>13606</v>
       </c>
       <c r="I12" t="n">
-        <v>29146</v>
+        <v>13768</v>
       </c>
       <c r="J12" t="n">
-        <v>29210</v>
+        <v>14199</v>
       </c>
       <c r="K12" t="n">
-        <v>28994</v>
+        <v>14469</v>
       </c>
       <c r="L12" t="n">
-        <v>28834</v>
+        <v>14447</v>
       </c>
       <c r="M12" t="n">
-        <v>23949</v>
+        <v>13677</v>
       </c>
       <c r="N12" t="n">
-        <v>23010</v>
+        <v>13398</v>
       </c>
       <c r="O12" t="n">
-        <v>22623</v>
+        <v>12992</v>
       </c>
       <c r="P12" t="n">
-        <v>22406</v>
+        <v>12918</v>
       </c>
       <c r="Q12" t="n">
-        <v>22341</v>
+        <v>12978</v>
       </c>
       <c r="R12" t="n">
-        <v>20870</v>
+        <v>12598</v>
       </c>
       <c r="S12" t="n">
-        <v>20824</v>
+        <v>11946</v>
       </c>
       <c r="T12" t="n">
-        <v>20734</v>
+        <v>11567</v>
+      </c>
+      <c r="U12" t="n">
+        <v>11219</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Intangible Assets, Net (Excluding Goodwill)</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9444</v>
+        <v>57828</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>57774</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>33269</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>32335</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>32173</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>31935</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>29185</v>
       </c>
       <c r="I13" t="n">
-        <v>1833</v>
+        <v>29183</v>
       </c>
       <c r="J13" t="n">
-        <v>1966</v>
+        <v>29146</v>
       </c>
       <c r="K13" t="n">
-        <v>1968</v>
+        <v>29210</v>
       </c>
       <c r="L13" t="n">
-        <v>2192</v>
+        <v>28994</v>
       </c>
       <c r="M13" t="n">
-        <v>1377</v>
+        <v>28834</v>
       </c>
       <c r="N13" t="n">
-        <v>1313</v>
+        <v>23949</v>
       </c>
       <c r="O13" t="n">
-        <v>1549</v>
+        <v>23010</v>
       </c>
       <c r="P13" t="n">
-        <v>1626</v>
+        <v>22623</v>
       </c>
       <c r="Q13" t="n">
-        <v>1823</v>
+        <v>22406</v>
       </c>
       <c r="R13" t="n">
-        <v>1520</v>
+        <v>22341</v>
       </c>
       <c r="S13" t="n">
-        <v>1697</v>
+        <v>20870</v>
       </c>
       <c r="T13" t="n">
-        <v>1840</v>
+        <v>20824</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20734</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Other Assets, Noncurrent</t>
+          <t>Intangible Assets, Net (Excluding Goodwill)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17478</v>
+        <v>9105</v>
       </c>
       <c r="C14" t="n">
-        <v>16811</v>
+        <v>9444</v>
       </c>
       <c r="D14" t="n">
-        <v>14153</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>12950</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13867</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>9699</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>10065</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7628</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6822</v>
+        <v>1833</v>
       </c>
       <c r="K14" t="n">
-        <v>6439</v>
+        <v>1966</v>
       </c>
       <c r="L14" t="n">
-        <v>5670</v>
+        <v>1968</v>
       </c>
       <c r="M14" t="n">
-        <v>5712</v>
+        <v>2192</v>
       </c>
       <c r="N14" t="n">
-        <v>5778</v>
+        <v>1377</v>
       </c>
       <c r="O14" t="n">
-        <v>4276</v>
+        <v>1313</v>
       </c>
       <c r="P14" t="n">
-        <v>4298</v>
+        <v>1549</v>
       </c>
       <c r="Q14" t="n">
-        <v>4167</v>
+        <v>1626</v>
       </c>
       <c r="R14" t="n">
-        <v>3274</v>
+        <v>1823</v>
       </c>
       <c r="S14" t="n">
-        <v>2731</v>
+        <v>1520</v>
       </c>
       <c r="T14" t="n">
-        <v>2748</v>
+        <v>1697</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1840</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>Other Assets, Noncurrent</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>703919</v>
+        <v>39711</v>
       </c>
       <c r="C15" t="n">
-        <v>536469</v>
+        <v>17478</v>
       </c>
       <c r="D15" t="n">
-        <v>502053</v>
+        <v>16811</v>
       </c>
       <c r="E15" t="n">
-        <v>475374</v>
+        <v>14153</v>
       </c>
       <c r="F15" t="n">
-        <v>430266</v>
+        <v>12950</v>
       </c>
       <c r="G15" t="n">
-        <v>414770</v>
+        <v>13867</v>
       </c>
       <c r="H15" t="n">
-        <v>407350</v>
+        <v>9699</v>
       </c>
       <c r="I15" t="n">
-        <v>396711</v>
+        <v>10065</v>
       </c>
       <c r="J15" t="n">
-        <v>383044</v>
+        <v>7628</v>
       </c>
       <c r="K15" t="n">
-        <v>369491</v>
+        <v>6822</v>
       </c>
       <c r="L15" t="n">
-        <v>358255</v>
+        <v>6439</v>
       </c>
       <c r="M15" t="n">
-        <v>355185</v>
+        <v>5670</v>
       </c>
       <c r="N15" t="n">
-        <v>357096</v>
+        <v>5712</v>
       </c>
       <c r="O15" t="n">
-        <v>347403</v>
+        <v>5778</v>
       </c>
       <c r="P15" t="n">
-        <v>335387</v>
+        <v>4276</v>
       </c>
       <c r="Q15" t="n">
-        <v>327095</v>
+        <v>4298</v>
       </c>
       <c r="R15" t="n">
-        <v>299243</v>
+        <v>4167</v>
       </c>
       <c r="S15" t="n">
-        <v>278492</v>
+        <v>3274</v>
       </c>
       <c r="T15" t="n">
-        <v>273403</v>
+        <v>2731</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2748</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Accounts Payable, Current</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16852</v>
+        <v>921983</v>
       </c>
       <c r="C16" t="n">
-        <v>10546</v>
+        <v>703919</v>
       </c>
       <c r="D16" t="n">
-        <v>8347</v>
+        <v>536469</v>
       </c>
       <c r="E16" t="n">
-        <v>8497</v>
+        <v>502053</v>
       </c>
       <c r="F16" t="n">
-        <v>7049</v>
+        <v>475374</v>
       </c>
       <c r="G16" t="n">
-        <v>6092</v>
+        <v>430266</v>
       </c>
       <c r="H16" t="n">
-        <v>6198</v>
+        <v>414770</v>
       </c>
       <c r="I16" t="n">
-        <v>5803</v>
+        <v>407350</v>
       </c>
       <c r="J16" t="n">
-        <v>5313</v>
+        <v>396711</v>
       </c>
       <c r="K16" t="n">
-        <v>4184</v>
+        <v>383044</v>
       </c>
       <c r="L16" t="n">
-        <v>6303</v>
+        <v>369491</v>
       </c>
       <c r="M16" t="n">
-        <v>4409</v>
+        <v>358255</v>
       </c>
       <c r="N16" t="n">
-        <v>3436</v>
+        <v>355185</v>
       </c>
       <c r="O16" t="n">
-        <v>4616</v>
+        <v>357096</v>
       </c>
       <c r="P16" t="n">
-        <v>4708</v>
+        <v>347403</v>
       </c>
       <c r="Q16" t="n">
-        <v>4801</v>
+        <v>335387</v>
       </c>
       <c r="R16" t="n">
-        <v>4391</v>
+        <v>327095</v>
       </c>
       <c r="S16" t="n">
-        <v>4064</v>
+        <v>299243</v>
       </c>
       <c r="T16" t="n">
-        <v>4099</v>
+        <v>278492</v>
+      </c>
+      <c r="U16" t="n">
+        <v>273403</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Employee-related Liabilities, Current</t>
+          <t>Accounts Payable, Current</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13947</v>
+        <v>20258</v>
       </c>
       <c r="C17" t="n">
-        <v>13944</v>
+        <v>16852</v>
       </c>
       <c r="D17" t="n">
-        <v>12168</v>
+        <v>10546</v>
       </c>
       <c r="E17" t="n">
-        <v>9984</v>
+        <v>8347</v>
       </c>
       <c r="F17" t="n">
-        <v>12908</v>
+        <v>8497</v>
       </c>
       <c r="G17" t="n">
-        <v>11373</v>
+        <v>7049</v>
       </c>
       <c r="H17" t="n">
-        <v>9703</v>
+        <v>6092</v>
       </c>
       <c r="I17" t="n">
-        <v>12562</v>
+        <v>6198</v>
       </c>
       <c r="J17" t="n">
-        <v>11260</v>
+        <v>5803</v>
       </c>
       <c r="K17" t="n">
-        <v>9954</v>
+        <v>5313</v>
       </c>
       <c r="L17" t="n">
-        <v>12366</v>
+        <v>4184</v>
       </c>
       <c r="M17" t="n">
-        <v>10852</v>
+        <v>6303</v>
       </c>
       <c r="N17" t="n">
-        <v>9803</v>
+        <v>4409</v>
       </c>
       <c r="O17" t="n">
-        <v>12170</v>
+        <v>3436</v>
       </c>
       <c r="P17" t="n">
-        <v>10088</v>
+        <v>4616</v>
       </c>
       <c r="Q17" t="n">
-        <v>8375</v>
+        <v>4708</v>
       </c>
       <c r="R17" t="n">
-        <v>8747</v>
+        <v>4801</v>
       </c>
       <c r="S17" t="n">
-        <v>7127</v>
+        <v>4391</v>
       </c>
       <c r="T17" t="n">
-        <v>5656</v>
+        <v>4064</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4099</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Accrued Liabilities, Current</t>
+          <t>Employee-related Liabilities, Current</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63019</v>
+        <v>15086</v>
       </c>
       <c r="C18" t="n">
-        <v>59437</v>
+        <v>13947</v>
       </c>
       <c r="D18" t="n">
-        <v>52039</v>
+        <v>13944</v>
       </c>
       <c r="E18" t="n">
-        <v>58300</v>
+        <v>12168</v>
       </c>
       <c r="F18" t="n">
-        <v>46585</v>
+        <v>9984</v>
       </c>
       <c r="G18" t="n">
-        <v>47298</v>
+        <v>12908</v>
       </c>
       <c r="H18" t="n">
-        <v>48603</v>
+        <v>11373</v>
       </c>
       <c r="I18" t="n">
-        <v>55602</v>
+        <v>9703</v>
       </c>
       <c r="J18" t="n">
-        <v>49300</v>
+        <v>12562</v>
       </c>
       <c r="K18" t="n">
-        <v>43185</v>
+        <v>11260</v>
       </c>
       <c r="L18" t="n">
-        <v>35038</v>
+        <v>9954</v>
       </c>
       <c r="M18" t="n">
-        <v>32976</v>
+        <v>12366</v>
       </c>
       <c r="N18" t="n">
-        <v>33051</v>
+        <v>10852</v>
       </c>
       <c r="O18" t="n">
-        <v>30113</v>
+        <v>9803</v>
       </c>
       <c r="P18" t="n">
-        <v>28981</v>
+        <v>12170</v>
       </c>
       <c r="Q18" t="n">
-        <v>30732</v>
+        <v>10088</v>
       </c>
       <c r="R18" t="n">
-        <v>25631</v>
+        <v>8375</v>
       </c>
       <c r="S18" t="n">
-        <v>24426</v>
+        <v>8747</v>
       </c>
       <c r="T18" t="n">
-        <v>22601</v>
+        <v>7127</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Accrued Revenue Share</t>
+          <t>Accrued Liabilities, Current</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10208</v>
+        <v>73014</v>
       </c>
       <c r="C19" t="n">
-        <v>10081</v>
+        <v>63019</v>
       </c>
       <c r="D19" t="n">
-        <v>9787</v>
+        <v>59437</v>
       </c>
       <c r="E19" t="n">
-        <v>9965</v>
+        <v>52039</v>
       </c>
       <c r="F19" t="n">
-        <v>9365</v>
+        <v>58300</v>
       </c>
       <c r="G19" t="n">
-        <v>8899</v>
+        <v>46585</v>
       </c>
       <c r="H19" t="n">
-        <v>8520</v>
+        <v>47298</v>
       </c>
       <c r="I19" t="n">
-        <v>8025</v>
+        <v>48603</v>
       </c>
       <c r="J19" t="n">
-        <v>7990</v>
+        <v>55602</v>
       </c>
       <c r="K19" t="n">
-        <v>7816</v>
+        <v>49300</v>
       </c>
       <c r="L19" t="n">
-        <v>7662</v>
+        <v>43185</v>
       </c>
       <c r="M19" t="n">
-        <v>7889</v>
+        <v>35038</v>
       </c>
       <c r="N19" t="n">
-        <v>8116</v>
+        <v>32976</v>
       </c>
       <c r="O19" t="n">
-        <v>7745</v>
+        <v>33051</v>
       </c>
       <c r="P19" t="n">
-        <v>7438</v>
+        <v>30113</v>
       </c>
       <c r="Q19" t="n">
-        <v>6962</v>
+        <v>28981</v>
       </c>
       <c r="R19" t="n">
-        <v>6030</v>
+        <v>30732</v>
       </c>
       <c r="S19" t="n">
-        <v>5005</v>
+        <v>25631</v>
       </c>
       <c r="T19" t="n">
-        <v>4982</v>
+        <v>24426</v>
+      </c>
+      <c r="U19" t="n">
+        <v>22601</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Contract with Customer, Liability, Current</t>
+          <t>Accrued Revenue Share</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7162</v>
+        <v>10599</v>
       </c>
       <c r="C20" t="n">
-        <v>5542</v>
+        <v>10208</v>
       </c>
       <c r="D20" t="n">
-        <v>4969</v>
+        <v>10081</v>
       </c>
       <c r="E20" t="n">
-        <v>4908</v>
+        <v>9787</v>
       </c>
       <c r="F20" t="n">
-        <v>4896</v>
+        <v>9965</v>
       </c>
       <c r="G20" t="n">
-        <v>4251</v>
+        <v>9365</v>
       </c>
       <c r="H20" t="n">
-        <v>3973</v>
+        <v>8899</v>
       </c>
       <c r="I20" t="n">
-        <v>4303</v>
+        <v>8520</v>
       </c>
       <c r="J20" t="n">
-        <v>3846</v>
+        <v>8025</v>
       </c>
       <c r="K20" t="n">
-        <v>3715</v>
+        <v>7990</v>
       </c>
       <c r="L20" t="n">
-        <v>3585</v>
+        <v>7816</v>
       </c>
       <c r="M20" t="n">
-        <v>3272</v>
+        <v>7662</v>
       </c>
       <c r="N20" t="n">
-        <v>3198</v>
+        <v>7889</v>
       </c>
       <c r="O20" t="n">
-        <v>2968</v>
+        <v>8116</v>
       </c>
       <c r="P20" t="n">
-        <v>2715</v>
+        <v>7745</v>
       </c>
       <c r="Q20" t="n">
-        <v>2690</v>
+        <v>7438</v>
       </c>
       <c r="R20" t="n">
-        <v>2302</v>
+        <v>6962</v>
       </c>
       <c r="S20" t="n">
-        <v>2061</v>
+        <v>6030</v>
       </c>
       <c r="T20" t="n">
-        <v>1938</v>
+        <v>5005</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Liabilities, Current</t>
+          <t>Contract with Customer, Liability, Current</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111188</v>
+        <v>7154</v>
       </c>
       <c r="C21" t="n">
-        <v>99550</v>
+        <v>7162</v>
       </c>
       <c r="D21" t="n">
-        <v>87310</v>
+        <v>5542</v>
       </c>
       <c r="E21" t="n">
-        <v>91654</v>
+        <v>4969</v>
       </c>
       <c r="F21" t="n">
-        <v>80803</v>
+        <v>4908</v>
       </c>
       <c r="G21" t="n">
-        <v>77913</v>
+        <v>4896</v>
       </c>
       <c r="H21" t="n">
-        <v>76997</v>
+        <v>4251</v>
       </c>
       <c r="I21" t="n">
-        <v>86295</v>
+        <v>3973</v>
       </c>
       <c r="J21" t="n">
-        <v>77709</v>
+        <v>4303</v>
       </c>
       <c r="K21" t="n">
-        <v>68854</v>
+        <v>3846</v>
       </c>
       <c r="L21" t="n">
-        <v>65979</v>
+        <v>3715</v>
       </c>
       <c r="M21" t="n">
-        <v>61354</v>
+        <v>3585</v>
       </c>
       <c r="N21" t="n">
-        <v>61948</v>
+        <v>3272</v>
       </c>
       <c r="O21" t="n">
-        <v>61782</v>
+        <v>3198</v>
       </c>
       <c r="P21" t="n">
-        <v>55741</v>
+        <v>2968</v>
       </c>
       <c r="Q21" t="n">
-        <v>55453</v>
+        <v>2715</v>
       </c>
       <c r="R21" t="n">
-        <v>48200</v>
+        <v>2690</v>
       </c>
       <c r="S21" t="n">
-        <v>43658</v>
+        <v>2302</v>
       </c>
       <c r="T21" t="n">
-        <v>40189</v>
+        <v>2061</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1938</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Accrued Income Taxes, Noncurrent</t>
+          <t>Liabilities, Current</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12457</v>
+        <v>126111</v>
       </c>
       <c r="C22" t="n">
-        <v>10072</v>
+        <v>111188</v>
       </c>
       <c r="D22" t="n">
-        <v>10027</v>
+        <v>99550</v>
       </c>
       <c r="E22" t="n">
-        <v>9773</v>
+        <v>87310</v>
       </c>
       <c r="F22" t="n">
-        <v>8219</v>
+        <v>91654</v>
       </c>
       <c r="G22" t="n">
-        <v>7703</v>
+        <v>80803</v>
       </c>
       <c r="H22" t="n">
-        <v>9234</v>
+        <v>77913</v>
       </c>
       <c r="I22" t="n">
-        <v>8038</v>
+        <v>76997</v>
       </c>
       <c r="J22" t="n">
-        <v>8753</v>
+        <v>86295</v>
       </c>
       <c r="K22" t="n">
-        <v>9722</v>
+        <v>77709</v>
       </c>
       <c r="L22" t="n">
-        <v>8572</v>
+        <v>68854</v>
       </c>
       <c r="M22" t="n">
-        <v>8163</v>
+        <v>65979</v>
       </c>
       <c r="N22" t="n">
-        <v>9406</v>
+        <v>61354</v>
       </c>
       <c r="O22" t="n">
-        <v>8984</v>
+        <v>61948</v>
       </c>
       <c r="P22" t="n">
-        <v>8651</v>
+        <v>61782</v>
       </c>
       <c r="Q22" t="n">
-        <v>9278</v>
+        <v>55741</v>
       </c>
       <c r="R22" t="n">
-        <v>8616</v>
+        <v>55453</v>
       </c>
       <c r="S22" t="n">
-        <v>8599</v>
+        <v>48200</v>
       </c>
       <c r="T22" t="n">
-        <v>9207</v>
+        <v>43658</v>
+      </c>
+      <c r="U22" t="n">
+        <v>40189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease Liabilities</t>
+          <t>Accrued Income Taxes, Noncurrent</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12983</v>
+        <v>11306</v>
       </c>
       <c r="C23" t="n">
-        <v>12106</v>
+        <v>12457</v>
       </c>
       <c r="D23" t="n">
-        <v>11952</v>
+        <v>10072</v>
       </c>
       <c r="E23" t="n">
-        <v>11678</v>
+        <v>10027</v>
       </c>
       <c r="F23" t="n">
-        <v>11654</v>
+        <v>9773</v>
       </c>
       <c r="G23" t="n">
-        <v>11708</v>
+        <v>8219</v>
       </c>
       <c r="H23" t="n">
-        <v>11957</v>
+        <v>7703</v>
       </c>
       <c r="I23" t="n">
-        <v>12550</v>
+        <v>9234</v>
       </c>
       <c r="J23" t="n">
-        <v>12746</v>
+        <v>8038</v>
       </c>
       <c r="K23" t="n">
-        <v>12799</v>
+        <v>8753</v>
       </c>
       <c r="L23" t="n">
-        <v>11984</v>
+        <v>9722</v>
       </c>
       <c r="M23" t="n">
-        <v>11697</v>
+        <v>8572</v>
       </c>
       <c r="N23" t="n">
-        <v>11363</v>
+        <v>8163</v>
       </c>
       <c r="O23" t="n">
-        <v>11471</v>
+        <v>9406</v>
       </c>
       <c r="P23" t="n">
-        <v>11619</v>
+        <v>8984</v>
       </c>
       <c r="Q23" t="n">
-        <v>11382</v>
+        <v>8651</v>
       </c>
       <c r="R23" t="n">
-        <v>10984</v>
+        <v>9278</v>
       </c>
       <c r="S23" t="n">
-        <v>10709</v>
+        <v>8616</v>
       </c>
       <c r="T23" t="n">
-        <v>10476</v>
+        <v>8599</v>
+      </c>
+      <c r="U23" t="n">
+        <v>9207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Other Liabilities, Noncurrent</t>
+          <t>Deferred Income Tax Liabilities, Net</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11044</v>
+        <v>22819</v>
       </c>
       <c r="C24" t="n">
-        <v>6267</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>6241</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>6116</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1453</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1753</v>
+        <v>706</v>
       </c>
       <c r="H24" t="n">
-        <v>1683</v>
+        <v>717</v>
       </c>
       <c r="I24" t="n">
-        <v>1433</v>
+        <v>486</v>
       </c>
       <c r="J24" t="n">
-        <v>1765</v>
+        <v>528</v>
       </c>
       <c r="K24" t="n">
-        <v>2373</v>
+        <v>558</v>
       </c>
       <c r="L24" t="n">
-        <v>2371</v>
+        <v>542</v>
       </c>
       <c r="M24" t="n">
-        <v>2422</v>
+        <v>476</v>
       </c>
       <c r="N24" t="n">
-        <v>2242</v>
+        <v>924</v>
       </c>
       <c r="O24" t="n">
-        <v>2250</v>
+        <v>2843</v>
       </c>
       <c r="P24" t="n">
-        <v>2270</v>
+        <v>3551</v>
       </c>
       <c r="Q24" t="n">
-        <v>2146</v>
+        <v>4703</v>
       </c>
       <c r="R24" t="n">
-        <v>2194</v>
+        <v>4406</v>
       </c>
       <c r="S24" t="n">
-        <v>1992</v>
+        <v>1973</v>
       </c>
       <c r="T24" t="n">
-        <v>2427</v>
+        <v>1797</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2079</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Operating Lease Liabilities</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>225173</v>
+        <v>14591</v>
       </c>
       <c r="C25" t="n">
-        <v>149602</v>
+        <v>12983</v>
       </c>
       <c r="D25" t="n">
-        <v>139137</v>
+        <v>12106</v>
       </c>
       <c r="E25" t="n">
-        <v>130107</v>
+        <v>11952</v>
       </c>
       <c r="F25" t="n">
-        <v>116147</v>
+        <v>11678</v>
       </c>
       <c r="G25" t="n">
-        <v>114017</v>
+        <v>11654</v>
       </c>
       <c r="H25" t="n">
-        <v>114506</v>
+        <v>11708</v>
       </c>
       <c r="I25" t="n">
-        <v>123509</v>
+        <v>11957</v>
       </c>
       <c r="J25" t="n">
-        <v>115903</v>
+        <v>12550</v>
       </c>
       <c r="K25" t="n">
-        <v>108597</v>
+        <v>12746</v>
       </c>
       <c r="L25" t="n">
-        <v>104629</v>
+        <v>12799</v>
       </c>
       <c r="M25" t="n">
-        <v>99766</v>
+        <v>11984</v>
       </c>
       <c r="N25" t="n">
-        <v>103092</v>
+        <v>11697</v>
       </c>
       <c r="O25" t="n">
-        <v>102836</v>
+        <v>11363</v>
       </c>
       <c r="P25" t="n">
-        <v>97822</v>
+        <v>11471</v>
       </c>
       <c r="Q25" t="n">
-        <v>97082</v>
+        <v>11619</v>
       </c>
       <c r="R25" t="n">
-        <v>86323</v>
+        <v>11382</v>
       </c>
       <c r="S25" t="n">
-        <v>71170</v>
+        <v>10984</v>
       </c>
       <c r="T25" t="n">
-        <v>69744</v>
+        <v>10709</v>
+      </c>
+      <c r="U25" t="n">
+        <v>10476</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Common Stocks, Including Additional Paid in Capital</t>
+          <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>96902</v>
+        <v>8511</v>
       </c>
       <c r="C26" t="n">
-        <v>91695</v>
+        <v>11044</v>
       </c>
       <c r="D26" t="n">
-        <v>89283</v>
+        <v>6267</v>
       </c>
       <c r="E26" t="n">
-        <v>86725</v>
+        <v>6241</v>
       </c>
       <c r="F26" t="n">
-        <v>82030</v>
+        <v>6116</v>
       </c>
       <c r="G26" t="n">
-        <v>79732</v>
+        <v>1453</v>
       </c>
       <c r="H26" t="n">
-        <v>77913</v>
+        <v>1753</v>
       </c>
       <c r="I26" t="n">
-        <v>74591</v>
+        <v>1683</v>
       </c>
       <c r="J26" t="n">
-        <v>72248</v>
+        <v>1433</v>
       </c>
       <c r="K26" t="n">
-        <v>70269</v>
+        <v>1765</v>
       </c>
       <c r="L26" t="n">
-        <v>66258</v>
+        <v>2373</v>
       </c>
       <c r="M26" t="n">
-        <v>64402</v>
+        <v>2371</v>
       </c>
       <c r="N26" t="n">
-        <v>62832</v>
+        <v>2422</v>
       </c>
       <c r="O26" t="n">
-        <v>61193</v>
+        <v>2242</v>
       </c>
       <c r="P26" t="n">
-        <v>60436</v>
+        <v>2250</v>
       </c>
       <c r="Q26" t="n">
-        <v>59436</v>
+        <v>2270</v>
       </c>
       <c r="R26" t="n">
-        <v>57307</v>
+        <v>2146</v>
       </c>
       <c r="S26" t="n">
-        <v>55937</v>
+        <v>2194</v>
       </c>
       <c r="T26" t="n">
-        <v>53688</v>
+        <v>1992</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2427</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2180</v>
+        <v>281503</v>
       </c>
       <c r="C27" t="n">
-        <v>-2054</v>
+        <v>225173</v>
       </c>
       <c r="D27" t="n">
-        <v>-2127</v>
+        <v>149602</v>
       </c>
       <c r="E27" t="n">
-        <v>-4086</v>
+        <v>139137</v>
       </c>
       <c r="F27" t="n">
-        <v>-3228</v>
+        <v>130107</v>
       </c>
       <c r="G27" t="n">
-        <v>-5012</v>
+        <v>116147</v>
       </c>
       <c r="H27" t="n">
-        <v>-4839</v>
+        <v>114017</v>
       </c>
       <c r="I27" t="n">
-        <v>-7036</v>
+        <v>114506</v>
       </c>
       <c r="J27" t="n">
-        <v>-5991</v>
+        <v>123509</v>
       </c>
       <c r="K27" t="n">
-        <v>-6000</v>
+        <v>115903</v>
       </c>
       <c r="L27" t="n">
-        <v>-8852</v>
+        <v>108597</v>
       </c>
       <c r="M27" t="n">
-        <v>-5828</v>
+        <v>104629</v>
       </c>
       <c r="N27" t="n">
-        <v>-4049</v>
+        <v>99766</v>
       </c>
       <c r="O27" t="n">
-        <v>-408</v>
+        <v>103092</v>
       </c>
       <c r="P27" t="n">
-        <v>190</v>
+        <v>102836</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3</v>
+        <v>97822</v>
       </c>
       <c r="R27" t="n">
-        <v>46</v>
+        <v>97082</v>
       </c>
       <c r="S27" t="n">
-        <v>-296</v>
+        <v>86323</v>
       </c>
       <c r="T27" t="n">
-        <v>-1097</v>
+        <v>71170</v>
+      </c>
+      <c r="U27" t="n">
+        <v>69744</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Retained Earnings (Accumulated Deficit)</t>
+          <t>Common Stocks, Including Additional Paid in Capital</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>384024</v>
+        <v>131371</v>
       </c>
       <c r="C28" t="n">
-        <v>297226</v>
+        <v>96902</v>
       </c>
       <c r="D28" t="n">
-        <v>275760</v>
+        <v>91695</v>
       </c>
       <c r="E28" t="n">
-        <v>262628</v>
+        <v>89283</v>
       </c>
       <c r="F28" t="n">
-        <v>235317</v>
+        <v>86725</v>
       </c>
       <c r="G28" t="n">
-        <v>226033</v>
+        <v>82030</v>
       </c>
       <c r="H28" t="n">
-        <v>219770</v>
+        <v>79732</v>
       </c>
       <c r="I28" t="n">
-        <v>205647</v>
+        <v>77913</v>
       </c>
       <c r="J28" t="n">
-        <v>200884</v>
+        <v>74591</v>
       </c>
       <c r="K28" t="n">
-        <v>196625</v>
+        <v>72248</v>
       </c>
       <c r="L28" t="n">
-        <v>196220</v>
+        <v>70269</v>
       </c>
       <c r="M28" t="n">
-        <v>196845</v>
+        <v>66258</v>
       </c>
       <c r="N28" t="n">
-        <v>195221</v>
+        <v>64402</v>
       </c>
       <c r="O28" t="n">
-        <v>183782</v>
+        <v>62832</v>
       </c>
       <c r="P28" t="n">
-        <v>176939</v>
+        <v>61193</v>
       </c>
       <c r="Q28" t="n">
-        <v>170580</v>
+        <v>60436</v>
       </c>
       <c r="R28" t="n">
-        <v>155567</v>
+        <v>59436</v>
       </c>
       <c r="S28" t="n">
-        <v>151681</v>
+        <v>57307</v>
       </c>
       <c r="T28" t="n">
-        <v>151068</v>
+        <v>55937</v>
+      </c>
+      <c r="U28" t="n">
+        <v>53688</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Total Shareholders Equity</t>
+          <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>478746</v>
+        <v>-2285</v>
       </c>
       <c r="C29" t="n">
-        <v>386867</v>
+        <v>-2180</v>
       </c>
       <c r="D29" t="n">
-        <v>362916</v>
+        <v>-2054</v>
       </c>
       <c r="E29" t="n">
-        <v>345267</v>
+        <v>-2127</v>
       </c>
       <c r="F29" t="n">
-        <v>314119</v>
+        <v>-4086</v>
       </c>
       <c r="G29" t="n">
-        <v>300753</v>
+        <v>-3228</v>
       </c>
       <c r="H29" t="n">
-        <v>292844</v>
+        <v>-5012</v>
       </c>
       <c r="I29" t="n">
-        <v>273202</v>
+        <v>-4839</v>
       </c>
       <c r="J29" t="n">
-        <v>267141</v>
+        <v>-7036</v>
       </c>
       <c r="K29" t="n">
-        <v>260894</v>
+        <v>-5991</v>
       </c>
       <c r="L29" t="n">
-        <v>253626</v>
+        <v>-6000</v>
       </c>
       <c r="M29" t="n">
-        <v>255419</v>
+        <v>-8852</v>
       </c>
       <c r="N29" t="n">
-        <v>254004</v>
+        <v>-5828</v>
       </c>
       <c r="O29" t="n">
-        <v>244567</v>
+        <v>-4049</v>
       </c>
       <c r="P29" t="n">
-        <v>237565</v>
+        <v>-408</v>
       </c>
       <c r="Q29" t="n">
-        <v>230013</v>
+        <v>190</v>
       </c>
       <c r="R29" t="n">
-        <v>212920</v>
+        <v>-3</v>
       </c>
       <c r="S29" t="n">
-        <v>207322</v>
+        <v>46</v>
       </c>
       <c r="T29" t="n">
-        <v>203659</v>
+        <v>-296</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-1097</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Long-term Debt</t>
+          <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>77501</v>
+        <v>493371</v>
       </c>
       <c r="C30" t="n">
-        <v>21607</v>
+        <v>384024</v>
       </c>
       <c r="D30" t="n">
-        <v>23607</v>
+        <v>297226</v>
       </c>
       <c r="E30" t="n">
-        <v>10886</v>
+        <v>275760</v>
       </c>
       <c r="F30" t="n">
-        <v>12297</v>
+        <v>262628</v>
       </c>
       <c r="G30" t="n">
-        <v>13238</v>
+        <v>235317</v>
       </c>
       <c r="H30" t="n">
-        <v>13228</v>
+        <v>226033</v>
       </c>
       <c r="I30" t="n">
-        <v>13781</v>
+        <v>219770</v>
       </c>
       <c r="J30" t="n">
-        <v>13705</v>
+        <v>205647</v>
       </c>
       <c r="K30" t="n">
-        <v>13697</v>
+        <v>200884</v>
       </c>
       <c r="L30" t="n">
-        <v>14653</v>
+        <v>196625</v>
       </c>
       <c r="M30" t="n">
-        <v>14734</v>
+        <v>196220</v>
       </c>
       <c r="N30" t="n">
-        <v>14791</v>
+        <v>196845</v>
       </c>
       <c r="O30" t="n">
-        <v>14288</v>
+        <v>195221</v>
       </c>
       <c r="P30" t="n">
-        <v>14328</v>
+        <v>183782</v>
       </c>
       <c r="Q30" t="n">
-        <v>13887</v>
+        <v>176939</v>
       </c>
       <c r="R30" t="n">
-        <v>13902</v>
+        <v>170580</v>
       </c>
       <c r="S30" t="n">
-        <v>4018</v>
+        <v>155567</v>
       </c>
       <c r="T30" t="n">
-        <v>5016</v>
+        <v>151681</v>
+      </c>
+      <c r="U30" t="n">
+        <v>151068</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Contract with Customer, Liability, Noncurrent</t>
+          <t>Total Shareholders Equity</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>640480</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>478746</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>386867</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>362916</v>
       </c>
       <c r="F31" t="n">
-        <v>1015</v>
+        <v>345267</v>
       </c>
       <c r="G31" t="n">
-        <v>985</v>
+        <v>314119</v>
       </c>
       <c r="H31" t="n">
-        <v>921</v>
+        <v>300753</v>
       </c>
       <c r="I31" t="n">
-        <v>884</v>
+        <v>292844</v>
       </c>
       <c r="J31" t="n">
-        <v>667</v>
+        <v>273202</v>
       </c>
       <c r="K31" t="n">
-        <v>610</v>
+        <v>267141</v>
       </c>
       <c r="L31" t="n">
-        <v>594</v>
+        <v>260894</v>
       </c>
       <c r="M31" t="n">
-        <v>472</v>
+        <v>253626</v>
       </c>
       <c r="N31" t="n">
-        <v>499</v>
+        <v>255419</v>
       </c>
       <c r="O31" t="n">
-        <v>510</v>
+        <v>254004</v>
       </c>
       <c r="P31" t="n">
-        <v>510</v>
+        <v>244567</v>
       </c>
       <c r="Q31" t="n">
-        <v>530</v>
+        <v>237565</v>
       </c>
       <c r="R31" t="n">
-        <v>454</v>
+        <v>230013</v>
       </c>
       <c r="S31" t="n">
-        <v>397</v>
+        <v>212920</v>
       </c>
       <c r="T31" t="n">
-        <v>350</v>
+        <v>207322</v>
+      </c>
+      <c r="U31" t="n">
+        <v>203659</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Liabilities, Net</t>
+          <t>Long-term Debt</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>98165</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>77501</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>21607</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>23607</v>
       </c>
       <c r="F32" t="n">
-        <v>706</v>
+        <v>10886</v>
       </c>
       <c r="G32" t="n">
-        <v>717</v>
+        <v>12297</v>
       </c>
       <c r="H32" t="n">
-        <v>486</v>
+        <v>13238</v>
       </c>
       <c r="I32" t="n">
-        <v>528</v>
+        <v>13228</v>
       </c>
       <c r="J32" t="n">
-        <v>558</v>
+        <v>13781</v>
       </c>
       <c r="K32" t="n">
-        <v>542</v>
+        <v>13705</v>
       </c>
       <c r="L32" t="n">
-        <v>476</v>
+        <v>13697</v>
       </c>
       <c r="M32" t="n">
-        <v>924</v>
+        <v>14653</v>
       </c>
       <c r="N32" t="n">
-        <v>2843</v>
+        <v>14734</v>
       </c>
       <c r="O32" t="n">
-        <v>3551</v>
+        <v>14791</v>
       </c>
       <c r="P32" t="n">
-        <v>4703</v>
+        <v>14288</v>
       </c>
       <c r="Q32" t="n">
-        <v>4406</v>
+        <v>14328</v>
       </c>
       <c r="R32" t="n">
-        <v>1973</v>
+        <v>13887</v>
       </c>
       <c r="S32" t="n">
-        <v>1797</v>
+        <v>13902</v>
       </c>
       <c r="T32" t="n">
-        <v>2079</v>
+        <v>4018</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5016</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Inventory, Net</t>
+          <t>Contract with Customer, Liability, Noncurrent</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2503,46 +2599,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1015</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="I33" t="n">
-        <v>2957</v>
+        <v>921</v>
       </c>
       <c r="J33" t="n">
-        <v>2231</v>
+        <v>884</v>
       </c>
       <c r="K33" t="n">
-        <v>2315</v>
+        <v>667</v>
       </c>
       <c r="L33" t="n">
-        <v>3156</v>
+        <v>610</v>
       </c>
       <c r="M33" t="n">
-        <v>1980</v>
+        <v>594</v>
       </c>
       <c r="N33" t="n">
-        <v>1369</v>
+        <v>472</v>
       </c>
       <c r="O33" t="n">
-        <v>1278</v>
+        <v>499</v>
       </c>
       <c r="P33" t="n">
-        <v>907</v>
+        <v>510</v>
       </c>
       <c r="Q33" t="n">
-        <v>888</v>
+        <v>510</v>
       </c>
       <c r="R33" t="n">
-        <v>835</v>
+        <v>530</v>
       </c>
       <c r="S33" t="n">
-        <v>815</v>
+        <v>454</v>
       </c>
       <c r="T33" t="n">
-        <v>889</v>
+        <v>397</v>
+      </c>
+      <c r="U33" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="34">
@@ -2582,30 +2681,33 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>1479</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>1366</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>919</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>753</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>884</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>493</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>588</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>394</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>1910</v>
       </c>
     </row>
@@ -2646,30 +2748,33 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1025</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>1956</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>4344</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>4170</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>1811</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>1893</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>1099</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>975</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>913</v>
       </c>
     </row>
@@ -2684,65 +2789,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -2753,60 +2861,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>119796</v>
+      </c>
+      <c r="C2" t="n">
         <v>109896</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>102346</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>96428</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>90234</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>88268</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>84742</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>80539</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>76693</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>74604</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>69787</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>69092</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>69685</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>68011</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>65118</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>61880</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>55314</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>46173</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>38297</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>41159</v>
       </c>
     </row>
@@ -2817,60 +2928,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>45943</v>
+      </c>
+      <c r="C3" t="n">
         <v>41271</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>41369</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>39039</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>36361</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>36474</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>35507</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>33712</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>33229</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>31916</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>30612</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>31158</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>30104</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>29599</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>27621</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>26227</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>24103</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>21117</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>18553</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>18982</v>
       </c>
     </row>
@@ -2881,60 +2995,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>18219</v>
+      </c>
+      <c r="C4" t="n">
         <v>17032</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>15151</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>13808</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>13556</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>12447</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>11860</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>11903</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>11258</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>10588</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>11468</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>10273</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>9841</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>9119</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7694</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>7675</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>7485</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>6856</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>6875</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>6820</v>
       </c>
     </row>
@@ -2945,60 +3062,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>8403</v>
+      </c>
+      <c r="C5" t="n">
         <v>7606</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>7205</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>7101</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6172</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>7227</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>6792</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>6426</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>6884</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>6781</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>6533</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6929</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6630</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>5825</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>5516</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>5276</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>4516</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>4231</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>3901</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -3009,60 +3129,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>6461</v>
+      </c>
+      <c r="C6" t="n">
         <v>4291</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>7393</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>5209</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>3539</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>3599</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>3158</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>3026</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>3979</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>3481</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>3759</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>3597</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>3657</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>3374</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>3256</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>3341</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>2773</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>2756</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>2585</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>2880</v>
       </c>
     </row>
@@ -3073,60 +3196,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>79026</v>
+      </c>
+      <c r="C7" t="n">
         <v>70200</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>71118</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>65157</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>59628</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>59747</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>57317</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>55067</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>55350</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>52766</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>52372</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>51957</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>50232</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>47917</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>44087</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>42519</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>38877</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>34960</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>31914</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>33182</v>
       </c>
     </row>
@@ -3137,60 +3263,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>40770</v>
+      </c>
+      <c r="C8" t="n">
         <v>39696</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>31228</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>31271</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>30606</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>28521</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>27425</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>25472</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>21343</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>21838</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>17415</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>17135</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>19453</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>20094</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>21031</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>19361</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>16437</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>11213</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>6383</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>7977</v>
       </c>
     </row>
@@ -3201,60 +3330,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="C9" t="n">
         <v>37716</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>12759</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2662</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>11183</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>3185</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>126</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>2843</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-146</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>65</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>790</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-902</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-439</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-1160</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2033</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>2624</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>4846</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>2146</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1894</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-220</v>
       </c>
     </row>
@@ -3265,60 +3397,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>138753</v>
+      </c>
+      <c r="C10" t="n">
         <v>77412</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>43987</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>33933</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>41789</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>31706</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>27551</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>28315</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>21197</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>21903</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>18205</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>16233</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>19014</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>18934</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>23064</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>21985</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>21283</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>13359</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>8277</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>7757</v>
       </c>
     </row>
@@ -3329,60 +3464,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>26560</v>
+      </c>
+      <c r="C11" t="n">
         <v>14834</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>9008</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>5737</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>7249</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>5405</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>3932</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4653</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1508</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>3535</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>3154</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2323</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>3012</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>2498</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>4128</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>3460</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>3353</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>2112</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>1318</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>921</v>
       </c>
     </row>
@@ -3393,188 +3531,331 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>112193</v>
+      </c>
+      <c r="C12" t="n">
         <v>62578</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>34979</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>28196</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>34540</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>26301</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>23619</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>23662</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>19689</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>18368</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>15051</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>13910</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>16002</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>16436</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>18936</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>18525</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>17930</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>11247</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>6959</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>6836</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Basic</t>
+          <t>Preferred Stock Dividends, Income Statement Impact</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.17</v>
+        <v>86</v>
       </c>
       <c r="C13" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>28.44</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>27.69</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26.63</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>16.55</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>10.21</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>9.960000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Net Income (Loss) Available to Common Stockholders, Basic</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>112107</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Earnings Per Share, Basic</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="R15" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="S15" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9.960000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="C16" t="n">
         <v>5.11</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D16" t="n">
         <v>2.87</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E16" t="n">
         <v>2.31</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F16" t="n">
         <v>2.81</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G16" t="n">
         <v>2.12</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H16" t="n">
         <v>1.89</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I16" t="n">
         <v>1.89</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J16" t="n">
         <v>1.55</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K16" t="n">
         <v>1.44</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L16" t="n">
         <v>1.17</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M16" t="n">
         <v>1.06</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N16" t="n">
         <v>1.21</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O16" t="n">
         <v>24.62</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P16" t="n">
         <v>27.99</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q16" t="n">
         <v>27.26</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R16" t="n">
         <v>26.29</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S16" t="n">
         <v>16.4</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T16" t="n">
         <v>10.13</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U16" t="n">
         <v>9.869999999999999</v>
       </c>
     </row>
@@ -3589,65 +3870,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -3658,60 +3942,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>174771</v>
+      </c>
+      <c r="C2" t="n">
         <v>62578</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>97715</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>62736</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>34540</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>73582</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>47281</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>23662</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>53108</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>33419</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>15051</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>46348</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>32438</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>16436</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>55391</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>36455</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>17930</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>25042</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>13795</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>6836</v>
       </c>
     </row>
@@ -3722,60 +4009,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>13586</v>
+      </c>
+      <c r="C3" t="n">
         <v>6482</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>15096</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>9485</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4487</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>11106</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>7121</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3413</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>10010</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6339</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3060</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>11222</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>7289</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>3591</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8340</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>5255</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2525</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>9366</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>6077</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2899</v>
       </c>
     </row>
@@ -3786,60 +4076,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>14708</v>
+      </c>
+      <c r="C4" t="n">
         <v>6751</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>17882</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>11514</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5516</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>16975</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>11129</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5264</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>16801</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>11058</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5284</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>14262</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>9286</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>4504</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>11422</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>7548</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>3745</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>9768</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>6573</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>3191</v>
       </c>
     </row>
@@ -3850,60 +4143,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>27538</v>
+      </c>
+      <c r="C5" t="n">
         <v>6920</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>7130</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>-1596</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-1152</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-3809</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-2738</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>419</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-6093</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>-4269</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>-1854</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-6157</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-4237</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>-2090</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>192</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1479</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1100</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>-280</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>-416</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>175</v>
       </c>
     </row>
@@ -3914,60 +4210,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-135803</v>
+      </c>
+      <c r="C6" t="n">
         <v>-36804</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-22266</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-11411</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-9960</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-2738</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-757</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-1781</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1294</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>425</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-84</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>3856</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>2478</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1437</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-9792</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>-7634</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>-4751</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-3055</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-1040</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>802</v>
       </c>
     </row>
@@ -3978,60 +4277,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3161</v>
+      </c>
+      <c r="C7" t="n">
         <v>1265</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>843</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1041</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>481</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2592</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1185</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>334</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>912</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>650</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>553</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>369</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>202</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>140</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-199</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-263</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-255</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>875</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>669</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>297</v>
       </c>
     </row>
@@ -4042,1788 +4344,2140 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-6904</v>
+      </c>
+      <c r="C8" t="n">
         <v>-363</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>-3582</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-1201</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1638</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-1321</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>110</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>3167</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-1315</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>1506</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>4454</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>2298</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2395</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>4364</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-3276</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-867</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>2794</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-1079</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>2522</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>2602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Income Taxes</t>
+          <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8101</v>
+        <v>-7739</v>
       </c>
       <c r="C9" t="n">
-        <v>-3292</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-2434</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7197</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-2797</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-889</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3011</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>10392</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>8520</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4069</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-862</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-253</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3820</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2744</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-297</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>469</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-245</v>
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Other Operating Assets</t>
+          <t>Increase (Decrease) in Income Taxes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-3403</v>
+        <v>8304</v>
       </c>
       <c r="C10" t="n">
-        <v>-4060</v>
+        <v>8101</v>
       </c>
       <c r="D10" t="n">
-        <v>-2767</v>
+        <v>-3292</v>
       </c>
       <c r="E10" t="n">
-        <v>-1288</v>
+        <v>-2434</v>
       </c>
       <c r="F10" t="n">
-        <v>-2334</v>
+        <v>7197</v>
       </c>
       <c r="G10" t="n">
-        <v>-1532</v>
+        <v>-2797</v>
       </c>
       <c r="H10" t="n">
-        <v>-1000</v>
+        <v>-889</v>
       </c>
       <c r="I10" t="n">
-        <v>-2883</v>
+        <v>3011</v>
       </c>
       <c r="J10" t="n">
-        <v>-1259</v>
+        <v>10392</v>
       </c>
       <c r="K10" t="n">
-        <v>-746</v>
+        <v>8520</v>
       </c>
       <c r="L10" t="n">
-        <v>-4268</v>
+        <v>4069</v>
       </c>
       <c r="M10" t="n">
-        <v>-1621</v>
+        <v>-862</v>
       </c>
       <c r="N10" t="n">
-        <v>-776</v>
+        <v>-253</v>
       </c>
       <c r="O10" t="n">
-        <v>-1447</v>
+        <v>3820</v>
       </c>
       <c r="P10" t="n">
-        <v>-192</v>
+        <v>2744</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>-297</v>
       </c>
       <c r="R10" t="n">
-        <v>-592</v>
+        <v>785</v>
       </c>
       <c r="S10" t="n">
-        <v>-359</v>
+        <v>469</v>
       </c>
       <c r="T10" t="n">
-        <v>-115</v>
+        <v>538</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accounts Payable</t>
+          <t>Increase (Decrease) in Other Operating Assets</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-240</v>
+        <v>-9950</v>
       </c>
       <c r="C11" t="n">
-        <v>-771</v>
+        <v>-3403</v>
       </c>
       <c r="D11" t="n">
-        <v>-327</v>
+        <v>-4060</v>
       </c>
       <c r="E11" t="n">
-        <v>-880</v>
+        <v>-2767</v>
       </c>
       <c r="F11" t="n">
-        <v>-42</v>
+        <v>-1288</v>
       </c>
       <c r="G11" t="n">
-        <v>-563</v>
+        <v>-2334</v>
       </c>
       <c r="H11" t="n">
-        <v>-2124</v>
+        <v>-1532</v>
       </c>
       <c r="I11" t="n">
-        <v>237</v>
+        <v>-1000</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>-2883</v>
       </c>
       <c r="K11" t="n">
-        <v>-1105</v>
+        <v>-1259</v>
       </c>
       <c r="L11" t="n">
-        <v>735</v>
+        <v>-746</v>
       </c>
       <c r="M11" t="n">
-        <v>-1172</v>
+        <v>-4268</v>
       </c>
       <c r="N11" t="n">
-        <v>-2373</v>
+        <v>-1621</v>
       </c>
       <c r="O11" t="n">
-        <v>-874</v>
+        <v>-776</v>
       </c>
       <c r="P11" t="n">
-        <v>-1112</v>
+        <v>-1447</v>
       </c>
       <c r="Q11" t="n">
-        <v>-982</v>
+        <v>-192</v>
       </c>
       <c r="R11" t="n">
-        <v>-269</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>-689</v>
+        <v>-592</v>
       </c>
       <c r="T11" t="n">
-        <v>-835</v>
+        <v>-359</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accrued Liabilities</t>
+          <t>Increase (Decrease) in Accounts Payable</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-6002</v>
+        <v>2090</v>
       </c>
       <c r="C12" t="n">
-        <v>6199</v>
+        <v>-240</v>
       </c>
       <c r="D12" t="n">
-        <v>-1560</v>
+        <v>-771</v>
       </c>
       <c r="E12" t="n">
-        <v>-5045</v>
+        <v>-327</v>
       </c>
       <c r="F12" t="n">
-        <v>-6366</v>
+        <v>-880</v>
       </c>
       <c r="G12" t="n">
-        <v>-5176</v>
+        <v>-42</v>
       </c>
       <c r="H12" t="n">
-        <v>-5054</v>
+        <v>-563</v>
       </c>
       <c r="I12" t="n">
-        <v>-380</v>
+        <v>-2124</v>
       </c>
       <c r="J12" t="n">
-        <v>-4037</v>
+        <v>237</v>
       </c>
       <c r="K12" t="n">
-        <v>-4496</v>
+        <v>14</v>
       </c>
       <c r="L12" t="n">
-        <v>491</v>
+        <v>-1105</v>
       </c>
       <c r="M12" t="n">
-        <v>-1719</v>
+        <v>735</v>
       </c>
       <c r="N12" t="n">
-        <v>-3216</v>
+        <v>-1172</v>
       </c>
       <c r="O12" t="n">
-        <v>2763</v>
+        <v>-2373</v>
       </c>
       <c r="P12" t="n">
-        <v>201</v>
+        <v>-874</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3530</v>
+        <v>-1112</v>
       </c>
       <c r="R12" t="n">
-        <v>891</v>
+        <v>-982</v>
       </c>
       <c r="S12" t="n">
-        <v>-2099</v>
+        <v>-269</v>
       </c>
       <c r="T12" t="n">
-        <v>-3531</v>
+        <v>-689</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-835</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Contract with Customer, Liability</t>
+          <t>Increase (Decrease) in Accrued Liabilities</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>505</v>
+        <v>308</v>
       </c>
       <c r="C13" t="n">
-        <v>1317</v>
+        <v>-6002</v>
       </c>
       <c r="D13" t="n">
-        <v>636</v>
+        <v>6199</v>
       </c>
       <c r="E13" t="n">
-        <v>500</v>
+        <v>-1560</v>
       </c>
       <c r="F13" t="n">
-        <v>860</v>
+        <v>-5045</v>
       </c>
       <c r="G13" t="n">
-        <v>220</v>
+        <v>-6366</v>
       </c>
       <c r="H13" t="n">
-        <v>-141</v>
+        <v>-5176</v>
       </c>
       <c r="I13" t="n">
-        <v>690</v>
+        <v>-5054</v>
       </c>
       <c r="J13" t="n">
-        <v>-17</v>
+        <v>-380</v>
       </c>
       <c r="K13" t="n">
-        <v>-201</v>
+        <v>-4037</v>
       </c>
       <c r="L13" t="n">
-        <v>104</v>
+        <v>-4496</v>
       </c>
       <c r="M13" t="n">
-        <v>-8</v>
+        <v>491</v>
       </c>
       <c r="N13" t="n">
-        <v>-94</v>
+        <v>-1719</v>
       </c>
       <c r="O13" t="n">
-        <v>406</v>
+        <v>-3216</v>
       </c>
       <c r="P13" t="n">
-        <v>134</v>
+        <v>2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="R13" t="n">
-        <v>428</v>
+        <v>-3530</v>
       </c>
       <c r="S13" t="n">
-        <v>148</v>
+        <v>891</v>
       </c>
       <c r="T13" t="n">
-        <v>37</v>
+        <v>-2099</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-3531</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Operating Activities</t>
+          <t>Increase (Decrease) in Contract with Customer, Liability</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45790</v>
+        <v>789</v>
       </c>
       <c r="C14" t="n">
-        <v>112311</v>
+        <v>505</v>
       </c>
       <c r="D14" t="n">
-        <v>63897</v>
+        <v>1317</v>
       </c>
       <c r="E14" t="n">
-        <v>36150</v>
+        <v>636</v>
       </c>
       <c r="F14" t="n">
-        <v>86186</v>
+        <v>500</v>
       </c>
       <c r="G14" t="n">
-        <v>55488</v>
+        <v>860</v>
       </c>
       <c r="H14" t="n">
-        <v>28848</v>
+        <v>220</v>
       </c>
       <c r="I14" t="n">
-        <v>82831</v>
+        <v>-141</v>
       </c>
       <c r="J14" t="n">
-        <v>52175</v>
+        <v>690</v>
       </c>
       <c r="K14" t="n">
-        <v>23509</v>
+        <v>-17</v>
       </c>
       <c r="L14" t="n">
-        <v>67881</v>
+        <v>-201</v>
       </c>
       <c r="M14" t="n">
-        <v>44528</v>
+        <v>104</v>
       </c>
       <c r="N14" t="n">
-        <v>25106</v>
+        <v>-8</v>
       </c>
       <c r="O14" t="n">
-        <v>66718</v>
+        <v>-94</v>
       </c>
       <c r="P14" t="n">
-        <v>41179</v>
+        <v>406</v>
       </c>
       <c r="Q14" t="n">
-        <v>19289</v>
+        <v>134</v>
       </c>
       <c r="R14" t="n">
-        <v>42447</v>
+        <v>137</v>
       </c>
       <c r="S14" t="n">
-        <v>25444</v>
+        <v>428</v>
       </c>
       <c r="T14" t="n">
-        <v>11451</v>
+        <v>148</v>
+      </c>
+      <c r="U14" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Purchases Of Property And Equipment And Intangible Assets</t>
+          <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-35674</v>
+        <v>84859</v>
       </c>
       <c r="C15" t="n">
-        <v>-63596</v>
+        <v>45790</v>
       </c>
       <c r="D15" t="n">
-        <v>-39643</v>
+        <v>112311</v>
       </c>
       <c r="E15" t="n">
-        <v>-17197</v>
+        <v>63897</v>
       </c>
       <c r="F15" t="n">
-        <v>-38259</v>
+        <v>36150</v>
       </c>
       <c r="G15" t="n">
-        <v>-25198</v>
+        <v>86186</v>
       </c>
       <c r="H15" t="n">
-        <v>-12012</v>
+        <v>55488</v>
       </c>
       <c r="I15" t="n">
-        <v>-21232</v>
+        <v>28848</v>
       </c>
       <c r="J15" t="n">
-        <v>-13177</v>
+        <v>82831</v>
       </c>
       <c r="K15" t="n">
-        <v>-6289</v>
+        <v>52175</v>
       </c>
       <c r="L15" t="n">
-        <v>-23890</v>
+        <v>23509</v>
       </c>
       <c r="M15" t="n">
-        <v>-16614</v>
+        <v>67881</v>
       </c>
       <c r="N15" t="n">
-        <v>-9786</v>
+        <v>44528</v>
       </c>
       <c r="O15" t="n">
-        <v>-18257</v>
+        <v>25106</v>
       </c>
       <c r="P15" t="n">
-        <v>-11438</v>
+        <v>66718</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5942</v>
+        <v>41179</v>
       </c>
       <c r="R15" t="n">
-        <v>-16802</v>
+        <v>19289</v>
       </c>
       <c r="S15" t="n">
-        <v>-11396</v>
+        <v>42447</v>
       </c>
       <c r="T15" t="n">
-        <v>-6005</v>
+        <v>25444</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11451</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Marketable Securities</t>
+          <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-31041</v>
+        <v>-80598</v>
       </c>
       <c r="C16" t="n">
-        <v>-60834</v>
+        <v>-35674</v>
       </c>
       <c r="D16" t="n">
-        <v>-39870</v>
+        <v>-63596</v>
       </c>
       <c r="E16" t="n">
-        <v>-18453</v>
+        <v>-39643</v>
       </c>
       <c r="F16" t="n">
-        <v>-65034</v>
+        <v>-17197</v>
       </c>
       <c r="G16" t="n">
-        <v>-43011</v>
+        <v>-38259</v>
       </c>
       <c r="H16" t="n">
-        <v>-20684</v>
+        <v>-25198</v>
       </c>
       <c r="I16" t="n">
-        <v>-49422</v>
+        <v>-12012</v>
       </c>
       <c r="J16" t="n">
-        <v>-35589</v>
+        <v>-21232</v>
       </c>
       <c r="K16" t="n">
-        <v>-14227</v>
+        <v>-13177</v>
       </c>
       <c r="L16" t="n">
-        <v>-67253</v>
+        <v>-6289</v>
       </c>
       <c r="M16" t="n">
-        <v>-50199</v>
+        <v>-23890</v>
       </c>
       <c r="N16" t="n">
-        <v>-28462</v>
+        <v>-16614</v>
       </c>
       <c r="O16" t="n">
-        <v>-95106</v>
+        <v>-9786</v>
       </c>
       <c r="P16" t="n">
-        <v>-60609</v>
+        <v>-18257</v>
       </c>
       <c r="Q16" t="n">
-        <v>-36426</v>
+        <v>-11438</v>
       </c>
       <c r="R16" t="n">
-        <v>-104932</v>
+        <v>-5942</v>
       </c>
       <c r="S16" t="n">
-        <v>-64111</v>
+        <v>-16802</v>
       </c>
       <c r="T16" t="n">
-        <v>-37563</v>
+        <v>-11396</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-6005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale and Maturity of Marketable Securities</t>
+          <t>Payments to Acquire Marketable Securities</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38001</v>
+        <v>-76480</v>
       </c>
       <c r="C17" t="n">
-        <v>61301</v>
+        <v>-31041</v>
       </c>
       <c r="D17" t="n">
-        <v>40930</v>
+        <v>-60834</v>
       </c>
       <c r="E17" t="n">
-        <v>20345</v>
+        <v>-39870</v>
       </c>
       <c r="F17" t="n">
-        <v>81779</v>
+        <v>-18453</v>
       </c>
       <c r="G17" t="n">
-        <v>58577</v>
+        <v>-65034</v>
       </c>
       <c r="H17" t="n">
-        <v>24985</v>
+        <v>-43011</v>
       </c>
       <c r="I17" t="n">
-        <v>52642</v>
+        <v>-20684</v>
       </c>
       <c r="J17" t="n">
-        <v>37049</v>
+        <v>-49422</v>
       </c>
       <c r="K17" t="n">
-        <v>18327</v>
+        <v>-35589</v>
       </c>
       <c r="L17" t="n">
-        <v>84087</v>
+        <v>-14227</v>
       </c>
       <c r="M17" t="n">
-        <v>55374</v>
+        <v>-67253</v>
       </c>
       <c r="N17" t="n">
-        <v>29779</v>
+        <v>-50199</v>
       </c>
       <c r="O17" t="n">
-        <v>92126</v>
+        <v>-28462</v>
       </c>
       <c r="P17" t="n">
-        <v>60667</v>
+        <v>-95106</v>
       </c>
       <c r="Q17" t="n">
-        <v>39248</v>
+        <v>-60609</v>
       </c>
       <c r="R17" t="n">
-        <v>97751</v>
+        <v>-36426</v>
       </c>
       <c r="S17" t="n">
-        <v>65874</v>
+        <v>-104932</v>
       </c>
       <c r="T17" t="n">
-        <v>41811</v>
+        <v>-64111</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-37563</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Other Investments</t>
+          <t>Proceeds from Sale and Maturity of Marketable Securities</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-906</v>
+        <v>66696</v>
       </c>
       <c r="C18" t="n">
-        <v>-3312</v>
+        <v>38001</v>
       </c>
       <c r="D18" t="n">
-        <v>-2312</v>
+        <v>61301</v>
       </c>
       <c r="E18" t="n">
-        <v>-958</v>
+        <v>40930</v>
       </c>
       <c r="F18" t="n">
-        <v>-3234</v>
+        <v>20345</v>
       </c>
       <c r="G18" t="n">
-        <v>-2199</v>
+        <v>81779</v>
       </c>
       <c r="H18" t="n">
-        <v>-1206</v>
+        <v>58577</v>
       </c>
       <c r="I18" t="n">
-        <v>-2176</v>
+        <v>24985</v>
       </c>
       <c r="J18" t="n">
-        <v>-1513</v>
+        <v>52642</v>
       </c>
       <c r="K18" t="n">
-        <v>-626</v>
+        <v>37049</v>
       </c>
       <c r="L18" t="n">
-        <v>-1628</v>
+        <v>18327</v>
       </c>
       <c r="M18" t="n">
-        <v>-1264</v>
+        <v>84087</v>
       </c>
       <c r="N18" t="n">
-        <v>-776</v>
+        <v>55374</v>
       </c>
       <c r="O18" t="n">
-        <v>-2068</v>
+        <v>29779</v>
       </c>
       <c r="P18" t="n">
-        <v>-1412</v>
+        <v>92126</v>
       </c>
       <c r="Q18" t="n">
-        <v>-646</v>
+        <v>60667</v>
       </c>
       <c r="R18" t="n">
-        <v>-1864</v>
+        <v>39248</v>
       </c>
       <c r="S18" t="n">
-        <v>-1311</v>
+        <v>97751</v>
       </c>
       <c r="T18" t="n">
-        <v>-572</v>
+        <v>65874</v>
+      </c>
+      <c r="U18" t="n">
+        <v>41811</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale and Maturity of Other Investments</t>
+          <t>Payments to Acquire Other Investments</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>848</v>
+        <v>-22051</v>
       </c>
       <c r="C19" t="n">
-        <v>1196</v>
+        <v>-906</v>
       </c>
       <c r="D19" t="n">
-        <v>873</v>
+        <v>-3312</v>
       </c>
       <c r="E19" t="n">
-        <v>259</v>
+        <v>-2312</v>
       </c>
       <c r="F19" t="n">
-        <v>732</v>
+        <v>-958</v>
       </c>
       <c r="G19" t="n">
-        <v>605</v>
+        <v>-3234</v>
       </c>
       <c r="H19" t="n">
-        <v>313</v>
+        <v>-2199</v>
       </c>
       <c r="I19" t="n">
-        <v>743</v>
+        <v>-1206</v>
       </c>
       <c r="J19" t="n">
-        <v>181</v>
+        <v>-2176</v>
       </c>
       <c r="K19" t="n">
-        <v>36</v>
+        <v>-1513</v>
       </c>
       <c r="L19" t="n">
-        <v>131</v>
+        <v>-626</v>
       </c>
       <c r="M19" t="n">
-        <v>125</v>
+        <v>-1628</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>-1264</v>
       </c>
       <c r="O19" t="n">
-        <v>590</v>
+        <v>-776</v>
       </c>
       <c r="P19" t="n">
-        <v>256</v>
+        <v>-2068</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>-1412</v>
       </c>
       <c r="R19" t="n">
-        <v>598</v>
+        <v>-646</v>
       </c>
       <c r="S19" t="n">
-        <v>473</v>
+        <v>-1864</v>
       </c>
       <c r="T19" t="n">
-        <v>260</v>
+        <v>-1311</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-572</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Acquisitions Net Of Cash Acquired And Purchases Of Intangible And Other Assets</t>
+          <t>Proceeds from Sale and Maturity of Other Investments</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-33621</v>
+        <v>1667</v>
       </c>
       <c r="C20" t="n">
-        <v>-1425</v>
+        <v>848</v>
       </c>
       <c r="D20" t="n">
-        <v>-353</v>
+        <v>1196</v>
       </c>
       <c r="E20" t="n">
-        <v>-340</v>
+        <v>873</v>
       </c>
       <c r="F20" t="n">
-        <v>-2840</v>
+        <v>259</v>
       </c>
       <c r="G20" t="n">
-        <v>-87</v>
+        <v>732</v>
       </c>
       <c r="H20" t="n">
-        <v>-61</v>
+        <v>605</v>
       </c>
       <c r="I20" t="n">
-        <v>-466</v>
+        <v>313</v>
       </c>
       <c r="J20" t="n">
-        <v>-340</v>
+        <v>743</v>
       </c>
       <c r="K20" t="n">
-        <v>-42</v>
+        <v>181</v>
       </c>
       <c r="L20" t="n">
-        <v>-6885</v>
+        <v>36</v>
       </c>
       <c r="M20" t="n">
-        <v>-1236</v>
+        <v>131</v>
       </c>
       <c r="N20" t="n">
-        <v>-173</v>
+        <v>125</v>
       </c>
       <c r="O20" t="n">
-        <v>-2233</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>-1974</v>
+        <v>590</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1666</v>
+        <v>256</v>
       </c>
       <c r="R20" t="n">
-        <v>-368</v>
+        <v>19</v>
       </c>
       <c r="S20" t="n">
-        <v>-355</v>
+        <v>598</v>
       </c>
       <c r="T20" t="n">
-        <v>-190</v>
+        <v>473</v>
+      </c>
+      <c r="U20" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Other Investing Activities</t>
+          <t>Acquisitions Net Of Cash Acquired And Purchases Of Intangible And Other Assets</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-996</v>
+        <v>-33697</v>
       </c>
       <c r="C21" t="n">
-        <v>-1845</v>
+        <v>-33621</v>
       </c>
       <c r="D21" t="n">
-        <v>-363</v>
+        <v>-1425</v>
       </c>
       <c r="E21" t="n">
-        <v>150</v>
+        <v>-353</v>
       </c>
       <c r="F21" t="n">
-        <v>-2500</v>
+        <v>-340</v>
       </c>
       <c r="G21" t="n">
-        <v>-32</v>
+        <v>-2840</v>
       </c>
       <c r="H21" t="n">
-        <v>101</v>
+        <v>-87</v>
       </c>
       <c r="I21" t="n">
-        <v>-985</v>
+        <v>-61</v>
       </c>
       <c r="J21" t="n">
-        <v>-357</v>
+        <v>-466</v>
       </c>
       <c r="K21" t="n">
-        <v>-125</v>
+        <v>-340</v>
       </c>
       <c r="L21" t="n">
-        <v>1367</v>
+        <v>-42</v>
       </c>
       <c r="M21" t="n">
-        <v>576</v>
+        <v>-6885</v>
       </c>
       <c r="N21" t="n">
-        <v>355</v>
+        <v>-1236</v>
       </c>
       <c r="O21" t="n">
-        <v>441</v>
+        <v>-173</v>
       </c>
       <c r="P21" t="n">
-        <v>53</v>
+        <v>-2233</v>
       </c>
       <c r="Q21" t="n">
-        <v>30</v>
+        <v>-1974</v>
       </c>
       <c r="R21" t="n">
-        <v>125</v>
+        <v>-1666</v>
       </c>
       <c r="S21" t="n">
-        <v>531</v>
+        <v>-368</v>
       </c>
       <c r="T21" t="n">
-        <v>412</v>
+        <v>-355</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-190</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Investing Activities</t>
+          <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-63389</v>
+        <v>-1359</v>
       </c>
       <c r="C22" t="n">
-        <v>-68515</v>
+        <v>-996</v>
       </c>
       <c r="D22" t="n">
-        <v>-40738</v>
+        <v>-1845</v>
       </c>
       <c r="E22" t="n">
-        <v>-16194</v>
+        <v>-363</v>
       </c>
       <c r="F22" t="n">
-        <v>-29356</v>
+        <v>150</v>
       </c>
       <c r="G22" t="n">
-        <v>-11345</v>
+        <v>-2500</v>
       </c>
       <c r="H22" t="n">
-        <v>-8564</v>
+        <v>-32</v>
       </c>
       <c r="I22" t="n">
-        <v>-20896</v>
+        <v>101</v>
       </c>
       <c r="J22" t="n">
-        <v>-13746</v>
+        <v>-985</v>
       </c>
       <c r="K22" t="n">
-        <v>-2946</v>
+        <v>-357</v>
       </c>
       <c r="L22" t="n">
-        <v>-14071</v>
+        <v>-125</v>
       </c>
       <c r="M22" t="n">
-        <v>-13238</v>
+        <v>1367</v>
       </c>
       <c r="N22" t="n">
-        <v>-9051</v>
+        <v>576</v>
       </c>
       <c r="O22" t="n">
-        <v>-24507</v>
+        <v>355</v>
       </c>
       <c r="P22" t="n">
-        <v>-14457</v>
+        <v>441</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5383</v>
+        <v>53</v>
       </c>
       <c r="R22" t="n">
-        <v>-25492</v>
+        <v>30</v>
       </c>
       <c r="S22" t="n">
-        <v>-10295</v>
+        <v>125</v>
       </c>
       <c r="T22" t="n">
-        <v>-1847</v>
+        <v>531</v>
+      </c>
+      <c r="U22" t="n">
+        <v>412</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Net Proceeds Payments Related To Stock Based Award Activities</t>
+          <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-5483</v>
+        <v>-145822</v>
       </c>
       <c r="C23" t="n">
-        <v>-9001</v>
+        <v>-63389</v>
       </c>
       <c r="D23" t="n">
-        <v>-5731</v>
+        <v>-68515</v>
       </c>
       <c r="E23" t="n">
-        <v>-3110</v>
+        <v>-40738</v>
       </c>
       <c r="F23" t="n">
-        <v>-9141</v>
+        <v>-16194</v>
       </c>
       <c r="G23" t="n">
-        <v>-6138</v>
+        <v>-29356</v>
       </c>
       <c r="H23" t="n">
-        <v>-2929</v>
+        <v>-11345</v>
       </c>
       <c r="I23" t="n">
-        <v>-7157</v>
+        <v>-8564</v>
       </c>
       <c r="J23" t="n">
-        <v>-4725</v>
+        <v>-20896</v>
       </c>
       <c r="K23" t="n">
-        <v>-1989</v>
+        <v>-13746</v>
       </c>
       <c r="L23" t="n">
-        <v>-7221</v>
+        <v>-2946</v>
       </c>
       <c r="M23" t="n">
-        <v>-5180</v>
+        <v>-14071</v>
       </c>
       <c r="N23" t="n">
-        <v>-2916</v>
+        <v>-13238</v>
       </c>
       <c r="O23" t="n">
-        <v>-7239</v>
+        <v>-9051</v>
       </c>
       <c r="P23" t="n">
-        <v>-4637</v>
+        <v>-24507</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2184</v>
+        <v>-14457</v>
       </c>
       <c r="R23" t="n">
-        <v>-4073</v>
+        <v>-5383</v>
       </c>
       <c r="S23" t="n">
-        <v>-2716</v>
+        <v>-25492</v>
       </c>
       <c r="T23" t="n">
-        <v>-1241</v>
+        <v>-10295</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-1847</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Net Proceeds Payments Related To Stock Based Award Activities</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>-12056</v>
       </c>
       <c r="C24" t="n">
-        <v>-40210</v>
+        <v>-5483</v>
       </c>
       <c r="D24" t="n">
-        <v>-28706</v>
+        <v>-9001</v>
       </c>
       <c r="E24" t="n">
-        <v>-15068</v>
+        <v>-5731</v>
       </c>
       <c r="F24" t="n">
-        <v>-46671</v>
+        <v>-3110</v>
       </c>
       <c r="G24" t="n">
-        <v>-31380</v>
+        <v>-9141</v>
       </c>
       <c r="H24" t="n">
-        <v>-15696</v>
+        <v>-6138</v>
       </c>
       <c r="I24" t="n">
-        <v>-45313</v>
+        <v>-2929</v>
       </c>
       <c r="J24" t="n">
-        <v>-29526</v>
+        <v>-7157</v>
       </c>
       <c r="K24" t="n">
-        <v>-14557</v>
+        <v>-4725</v>
       </c>
       <c r="L24" t="n">
-        <v>-43889</v>
+        <v>-1989</v>
       </c>
       <c r="M24" t="n">
-        <v>-28497</v>
+        <v>-7221</v>
       </c>
       <c r="N24" t="n">
-        <v>-13300</v>
+        <v>-5180</v>
       </c>
       <c r="O24" t="n">
-        <v>-36801</v>
+        <v>-2916</v>
       </c>
       <c r="P24" t="n">
-        <v>-24191</v>
+        <v>-7239</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11395</v>
+        <v>-4637</v>
       </c>
       <c r="R24" t="n">
-        <v>-23245</v>
+        <v>-2184</v>
       </c>
       <c r="S24" t="n">
-        <v>-15348</v>
+        <v>-4073</v>
       </c>
       <c r="T24" t="n">
-        <v>-8496</v>
+        <v>-2716</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-1241</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Payments of Dividends</t>
+          <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2542</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>-7513</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-4977</v>
+        <v>-40210</v>
       </c>
       <c r="E25" t="n">
-        <v>-2434</v>
+        <v>-28706</v>
       </c>
       <c r="F25" t="n">
-        <v>-4921</v>
+        <v>-15068</v>
       </c>
       <c r="G25" t="n">
-        <v>-2466</v>
+        <v>-46671</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-31380</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-15696</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-45313</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-29526</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-14557</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>-43889</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-28497</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>-13300</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-36801</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-24191</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>-11395</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-23245</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-15348</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-8496</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Debt, Net of Issuance Costs</t>
+          <t>Proceeds from Issuance of Common Stock</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31379</v>
+        <v>30499</v>
       </c>
       <c r="C26" t="n">
-        <v>38002</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>31378</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>4532</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>8694</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4875</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1982</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>9298</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>8050</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>6927</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>44322</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>29228</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>16422</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13949</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7599</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>11761</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1898</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1898</v>
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Debt and Lease Obligation</t>
+          <t>Proceeds from Issuance of Convertible Preferred Stock</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1477</v>
+        <v>19063</v>
       </c>
       <c r="C27" t="n">
-        <v>-26094</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-18397</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>-4521</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-8951</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-5502</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-3079</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-9621</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-8207</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-6952</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-45350</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-29582</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-16420</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>-15070</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-8678</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-937</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-2043</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-1982</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>-1947</v>
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Noncontrolling Interests</t>
+          <t>Proceeds from Debt, Net of Issuance Costs</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3200</v>
+        <v>56226</v>
       </c>
       <c r="C28" t="n">
-        <v>400</v>
+        <v>31379</v>
       </c>
       <c r="D28" t="n">
-        <v>400</v>
+        <v>38002</v>
       </c>
       <c r="E28" t="n">
-        <v>400</v>
+        <v>31378</v>
       </c>
       <c r="F28" t="n">
-        <v>293</v>
+        <v>4532</v>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>8694</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>4875</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>1982</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>9298</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>8050</v>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>6927</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>44322</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>29228</v>
       </c>
       <c r="O28" t="n">
-        <v>310</v>
+        <v>16422</v>
       </c>
       <c r="P28" t="n">
-        <v>310</v>
+        <v>13949</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>7599</v>
       </c>
       <c r="R28" t="n">
-        <v>2462</v>
+        <v>900</v>
       </c>
       <c r="S28" t="n">
-        <v>2464</v>
+        <v>11761</v>
       </c>
       <c r="T28" t="n">
-        <v>1600</v>
+        <v>1898</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1898</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Repayments of Debt and Lease Obligation</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25077</v>
+        <v>-5253</v>
       </c>
       <c r="C29" t="n">
-        <v>-44416</v>
+        <v>-1477</v>
       </c>
       <c r="D29" t="n">
-        <v>-26033</v>
+        <v>-26094</v>
       </c>
       <c r="E29" t="n">
-        <v>-20201</v>
+        <v>-18397</v>
       </c>
       <c r="F29" t="n">
-        <v>-60697</v>
+        <v>-4521</v>
       </c>
       <c r="G29" t="n">
-        <v>-40603</v>
+        <v>-8951</v>
       </c>
       <c r="H29" t="n">
-        <v>-19714</v>
+        <v>-5502</v>
       </c>
       <c r="I29" t="n">
-        <v>-52785</v>
+        <v>-3079</v>
       </c>
       <c r="J29" t="n">
-        <v>-34403</v>
+        <v>-9621</v>
       </c>
       <c r="K29" t="n">
-        <v>-16568</v>
+        <v>-8207</v>
       </c>
       <c r="L29" t="n">
-        <v>-52128</v>
+        <v>-6952</v>
       </c>
       <c r="M29" t="n">
-        <v>-34031</v>
+        <v>-45350</v>
       </c>
       <c r="N29" t="n">
-        <v>-16214</v>
+        <v>-29582</v>
       </c>
       <c r="O29" t="n">
-        <v>-44851</v>
+        <v>-16420</v>
       </c>
       <c r="P29" t="n">
-        <v>-29597</v>
+        <v>-15070</v>
       </c>
       <c r="Q29" t="n">
-        <v>-13606</v>
+        <v>-8678</v>
       </c>
       <c r="R29" t="n">
-        <v>-15138</v>
+        <v>-937</v>
       </c>
       <c r="S29" t="n">
-        <v>-15684</v>
+        <v>-2043</v>
       </c>
       <c r="T29" t="n">
-        <v>-8186</v>
+        <v>-1982</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-1947</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Proceeds from Noncontrolling Interests</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-123</v>
+        <v>3758</v>
       </c>
       <c r="C30" t="n">
-        <v>244</v>
+        <v>3200</v>
       </c>
       <c r="D30" t="n">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="E30" t="n">
-        <v>43</v>
+        <v>400</v>
       </c>
       <c r="F30" t="n">
-        <v>-222</v>
+        <v>400</v>
       </c>
       <c r="G30" t="n">
-        <v>-363</v>
+        <v>293</v>
       </c>
       <c r="H30" t="n">
-        <v>-125</v>
+        <v>8</v>
       </c>
       <c r="I30" t="n">
-        <v>-327</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
-        <v>-643</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>-268</v>
+        <v>10</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>-106</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="Q30" t="n">
-        <v>-143</v>
+        <v>310</v>
       </c>
       <c r="R30" t="n">
-        <v>-186</v>
+        <v>10</v>
       </c>
       <c r="S30" t="n">
-        <v>-221</v>
+        <v>2462</v>
       </c>
       <c r="T30" t="n">
-        <v>-272</v>
+        <v>2464</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7355</v>
+        <v>-686</v>
       </c>
       <c r="C31" t="n">
-        <v>-376</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-2430</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-202</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-4089</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3177</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>8823</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4050</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>4045</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1039</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-3009</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-59</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>-2746</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-2835</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1631</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>-756</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1146</v>
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30708</v>
+        <v>86320</v>
       </c>
       <c r="C32" t="n">
-        <v>23466</v>
+        <v>25077</v>
       </c>
       <c r="D32" t="n">
-        <v>23466</v>
+        <v>-44416</v>
       </c>
       <c r="E32" t="n">
-        <v>23466</v>
+        <v>-26033</v>
       </c>
       <c r="F32" t="n">
-        <v>24048</v>
+        <v>-20201</v>
       </c>
       <c r="G32" t="n">
-        <v>24048</v>
+        <v>-60697</v>
       </c>
       <c r="H32" t="n">
-        <v>24048</v>
+        <v>-40603</v>
       </c>
       <c r="I32" t="n">
-        <v>21879</v>
+        <v>-19714</v>
       </c>
       <c r="J32" t="n">
-        <v>21879</v>
+        <v>-52785</v>
       </c>
       <c r="K32" t="n">
-        <v>21879</v>
+        <v>-34403</v>
       </c>
       <c r="L32" t="n">
-        <v>20945</v>
+        <v>-16568</v>
       </c>
       <c r="M32" t="n">
-        <v>20945</v>
+        <v>-52128</v>
       </c>
       <c r="N32" t="n">
-        <v>20945</v>
+        <v>-34031</v>
       </c>
       <c r="O32" t="n">
-        <v>26465</v>
+        <v>-16214</v>
       </c>
       <c r="P32" t="n">
-        <v>26465</v>
+        <v>-44851</v>
       </c>
       <c r="Q32" t="n">
-        <v>26465</v>
+        <v>-29597</v>
       </c>
       <c r="R32" t="n">
-        <v>18498</v>
+        <v>-13606</v>
       </c>
       <c r="S32" t="n">
-        <v>18498</v>
+        <v>-15138</v>
       </c>
       <c r="T32" t="n">
-        <v>18498</v>
+        <v>-15684</v>
+      </c>
+      <c r="U32" t="n">
+        <v>-8186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Capital Expenditures Incurred but Not yet Paid</t>
+          <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24131</v>
+        <v>-154</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>-123</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-222</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-363</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-327</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>-643</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>-268</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>-143</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-186</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-221</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-272</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accrued Revenue Share</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>25203</v>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>7355</v>
       </c>
       <c r="D34" t="n">
-        <v>-219</v>
+        <v>-376</v>
       </c>
       <c r="E34" t="n">
-        <v>116</v>
+        <v>-2430</v>
       </c>
       <c r="F34" t="n">
-        <v>478</v>
+        <v>-202</v>
       </c>
       <c r="G34" t="n">
-        <v>97</v>
+        <v>-4089</v>
       </c>
       <c r="H34" t="n">
-        <v>-322</v>
+        <v>3177</v>
       </c>
       <c r="I34" t="n">
-        <v>-315</v>
+        <v>445</v>
       </c>
       <c r="J34" t="n">
-        <v>-418</v>
+        <v>8823</v>
       </c>
       <c r="K34" t="n">
-        <v>-602</v>
+        <v>4050</v>
       </c>
       <c r="L34" t="n">
-        <v>-1022</v>
+        <v>4045</v>
       </c>
       <c r="M34" t="n">
-        <v>-942</v>
+        <v>1039</v>
       </c>
       <c r="N34" t="n">
-        <v>-828</v>
+        <v>-3009</v>
       </c>
       <c r="O34" t="n">
-        <v>386</v>
+        <v>-59</v>
       </c>
       <c r="P34" t="n">
-        <v>29</v>
+        <v>-2746</v>
       </c>
       <c r="Q34" t="n">
-        <v>-444</v>
+        <v>-2835</v>
       </c>
       <c r="R34" t="n">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="S34" t="n">
-        <v>-692</v>
+        <v>1631</v>
       </c>
       <c r="T34" t="n">
-        <v>-871</v>
+        <v>-756</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1146</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30708</v>
+      </c>
+      <c r="C35" t="n">
+        <v>30708</v>
+      </c>
+      <c r="D35" t="n">
+        <v>23466</v>
+      </c>
+      <c r="E35" t="n">
+        <v>23466</v>
+      </c>
+      <c r="F35" t="n">
+        <v>23466</v>
+      </c>
+      <c r="G35" t="n">
+        <v>24048</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24048</v>
+      </c>
+      <c r="I35" t="n">
+        <v>24048</v>
+      </c>
+      <c r="J35" t="n">
+        <v>21879</v>
+      </c>
+      <c r="K35" t="n">
+        <v>21879</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21879</v>
+      </c>
+      <c r="M35" t="n">
+        <v>20945</v>
+      </c>
+      <c r="N35" t="n">
+        <v>20945</v>
+      </c>
+      <c r="O35" t="n">
+        <v>20945</v>
+      </c>
+      <c r="P35" t="n">
+        <v>26465</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>26465</v>
+      </c>
+      <c r="R35" t="n">
+        <v>26465</v>
+      </c>
+      <c r="S35" t="n">
+        <v>18498</v>
+      </c>
+      <c r="T35" t="n">
+        <v>18498</v>
+      </c>
+      <c r="U35" t="n">
+        <v>18498</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Capital Expenditures Incurred but Not yet Paid</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>29113</v>
+      </c>
+      <c r="C36" t="n">
+        <v>24131</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Payments of Dividends</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-5231</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-2542</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-7513</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-4977</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2434</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-4921</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-2466</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Increase (Decrease) in Accrued Revenue Share</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>100</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-219</v>
+      </c>
+      <c r="F38" t="n">
+        <v>116</v>
+      </c>
+      <c r="G38" t="n">
+        <v>478</v>
+      </c>
+      <c r="H38" t="n">
+        <v>97</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-322</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-315</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-418</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-602</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1022</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-942</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-828</v>
+      </c>
+      <c r="P38" t="n">
+        <v>386</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>29</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-444</v>
+      </c>
+      <c r="S38" t="n">
+        <v>277</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-692</v>
+      </c>
+      <c r="U38" t="n">
+        <v>-871</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>Amortization And Impairment Of Intangible Assets</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>373</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K39" t="n">
         <v>244</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L39" t="n">
         <v>126</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M39" t="n">
         <v>505</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N39" t="n">
         <v>392</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O39" t="n">
         <v>191</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P39" t="n">
         <v>662</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q39" t="n">
         <v>443</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R39" t="n">
         <v>228</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S39" t="n">
         <v>606</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T39" t="n">
         <v>417</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U39" t="n">
         <v>209</v>
       </c>
     </row>
@@ -5843,10 +6497,10 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="C1" s="1" t="n">
-        <v>45747</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="2">
@@ -5856,10 +6510,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>533</v>
+        <v>1278</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5873,65 +6527,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -5942,60 +6599,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>5836</v>
+      </c>
+      <c r="C2" t="n">
         <v>5822</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5818</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>5819</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>5831</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>5850</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5862</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5883</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5924</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5931</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>5949</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>5983</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>6015</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>300478</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>300519</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>300485</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>300800</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>300411</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>299308</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>300249</v>
       </c>
     </row>
@@ -6006,60 +6666,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>835</v>
+      </c>
+      <c r="C3" t="n">
         <v>837</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>845</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>852</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>859</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>865</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>866</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>869</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>875</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>879</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>883</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>885</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>887</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>44535</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>45404</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>45692</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>45840</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>46108</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>46355</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>46424</v>
       </c>
     </row>
@@ -6070,60 +6733,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>142</v>
+      </c>
+      <c r="C4" t="n">
         <v>139</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>117</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>76</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>108</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>129</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>152</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>112</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>115</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>96</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>42</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>79</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>106</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>14</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>15</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>18</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>47</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>92</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>180</v>
       </c>
     </row>
@@ -6134,60 +6800,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>5480</v>
+      </c>
+      <c r="C5" t="n">
         <v>5440</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>5423</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>5451</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>5493</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>5575</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>5615</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>5663</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>5782</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>5858</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>5949</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6150</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6231</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>315158</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>319835</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>322781</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>326580</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>332930</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>336105</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>339792</v>
       </c>
     </row>
